--- a/dance_registration_forms/026_dance_team_member_application_form--dance_registration_forms.xlsx
+++ b/dance_registration_forms/026_dance_team_member_application_form--dance_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
+          <t>emergency_contact_phone_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Contact Phone 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Emergency Contact Email</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>emergency_contact_relationship_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Emergency Contact Relationship 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'dancer'}</t>
+          <t>dancer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Dancer'}</t>
+          <t>Dancer</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'dancer'}</t>
+          <t>dancer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Dancer'}</t>
+          <t>Dancer</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'ballet'}</t>
+          <t>ballet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Ballet'}</t>
+          <t>Ballet</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'contemporary'}</t>
+          <t>contemporary</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Contemporary'}</t>
+          <t>Contemporary</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'hip_hop'}</t>
+          <t>hip_hop</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Hip Hop'}</t>
+          <t>Hip Hop</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'jazz'}</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Jazz'}</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'tap'}</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Tap'}</t>
+          <t>Tap</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'ballroom'}</t>
+          <t>ballroom</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Ballroom'}</t>
+          <t>Ballroom</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'latin'}</t>
+          <t>latin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Latin'}</t>
+          <t>Latin</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'advanced-advanced'}</t>
+          <t>advanced-advanced</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Advanced-Advanced'}</t>
+          <t>Advanced-Advanced</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'brother'}</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Brother'}</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'sister'}</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Sister'}</t>
+          <t>Sister</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1522,114 +1522,114 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'brother'}</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Brother'}</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'sister'}</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Sister'}</t>
+          <t>Sister</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
